--- a/template/input_template.xlsx
+++ b/template/input_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/didi/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/didi/Projects/zaccount/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC98C9EA-92E5-0B44-9F87-2B0A24EA38C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C13BA66-2383-F947-830C-7A3172673200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="860" windowWidth="28040" windowHeight="16620" xr2:uid="{3B4A8891-EA90-314F-B476-241F6EB57E07}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -58,6 +58,22 @@
   </si>
   <si>
     <t>desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>餐饮,午饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚餐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述（可选）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -104,8 +120,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -422,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAE0B06-48DA-A749-B091-EF361E515015}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -443,6 +462,26 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>45815</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
